--- a/astro-site/public/dl/kit-escandallos/10-calculadora-pvp.xlsx
+++ b/astro-site/public/dl/kit-escandallos/10-calculadora-pvp.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calculadora PVP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora PVP" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calculadora PVP'!$6:$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -153,56 +155,56 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -562,15 +564,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -592,6 +595,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -640,10 +644,19 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -651,7 +664,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -660,20 +682,21 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="16"/>
-    <col customWidth="1" max="6" min="6" width="16"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="9" t="inlineStr">
         <is>
@@ -681,6 +704,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="10" t="inlineStr">
         <is>
@@ -691,6 +715,7 @@
         <v>5.5</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="12" t="inlineStr">
         <is>
@@ -736,16 +761,16 @@
         <v>0.28</v>
       </c>
       <c r="E7" s="15">
-        <f>$C$4/=AVERAGE(C7,D7)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C7,D7)</f>
+        <v>20.754716981132074</v>
       </c>
       <c r="F7" s="16">
         <f>E7*1.10</f>
-        <v/>
+        <v>22.830188679245282</v>
       </c>
       <c r="G7" s="15">
         <f>E7-$C$4</f>
-        <v/>
+        <v>15.254716981132074</v>
       </c>
     </row>
     <row r="8">
@@ -761,16 +786,16 @@
         <v>0.32</v>
       </c>
       <c r="E8" s="19">
-        <f>$C$4/=AVERAGE(C8,D8)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C8,D8)</f>
+        <v>18.333333333333332</v>
       </c>
       <c r="F8" s="19">
         <f>E8*1.10</f>
-        <v/>
+        <v>20.166666666666668</v>
       </c>
       <c r="G8" s="19">
         <f>E8-$C$4</f>
-        <v/>
+        <v>12.833333333333332</v>
       </c>
     </row>
     <row r="9">
@@ -786,16 +811,16 @@
         <v>0.35</v>
       </c>
       <c r="E9" s="15">
-        <f>$C$4/=AVERAGE(C9,D9)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C9,D9)</f>
+        <v>16.923076923076927</v>
       </c>
       <c r="F9" s="15">
         <f>E9*1.10</f>
-        <v/>
+        <v>18.61538461538462</v>
       </c>
       <c r="G9" s="15">
         <f>E9-$C$4</f>
-        <v/>
+        <v>11.423076923076927</v>
       </c>
     </row>
     <row r="10">
@@ -811,16 +836,16 @@
         <v>0.3</v>
       </c>
       <c r="E10" s="19">
-        <f>$C$4/=AVERAGE(C10,D10)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C10,D10)</f>
+        <v>20.0</v>
       </c>
       <c r="F10" s="19">
         <f>E10*1.10</f>
-        <v/>
+        <v>22.0</v>
       </c>
       <c r="G10" s="19">
         <f>E10-$C$4</f>
-        <v/>
+        <v>14.5</v>
       </c>
     </row>
     <row r="11">
@@ -836,16 +861,16 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="15">
-        <f>$C$4/=AVERAGE(C11,D11)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C11,D11)</f>
+        <v>15.714285714285715</v>
       </c>
       <c r="F11" s="15">
         <f>E11*1.10</f>
-        <v/>
+        <v>17.28571428571429</v>
       </c>
       <c r="G11" s="15">
         <f>E11-$C$4</f>
-        <v/>
+        <v>10.214285714285715</v>
       </c>
     </row>
     <row r="12">
@@ -861,16 +886,16 @@
         <v>0.35</v>
       </c>
       <c r="E12" s="19">
-        <f>$C$4/=AVERAGE(C12,D12)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C12,D12)</f>
+        <v>17.46031746031746</v>
       </c>
       <c r="F12" s="19">
         <f>E12*1.10</f>
-        <v/>
+        <v>19.206349206349206</v>
       </c>
       <c r="G12" s="19">
         <f>E12-$C$4</f>
-        <v/>
+        <v>11.960317460317459</v>
       </c>
     </row>
     <row r="13">
@@ -886,16 +911,16 @@
         <v>0.35</v>
       </c>
       <c r="E13" s="15">
-        <f>$C$4/=AVERAGE(C13,D13)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C13,D13)</f>
+        <v>16.923076923076927</v>
       </c>
       <c r="F13" s="15">
         <f>E13*1.10</f>
-        <v/>
+        <v>18.61538461538462</v>
       </c>
       <c r="G13" s="15">
         <f>E13-$C$4</f>
-        <v/>
+        <v>11.423076923076927</v>
       </c>
     </row>
     <row r="14">
@@ -911,16 +936,16 @@
         <v>0.3</v>
       </c>
       <c r="E14" s="19">
-        <f>$C$4/=AVERAGE(C14,D14)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C14,D14)</f>
+        <v>22.0</v>
       </c>
       <c r="F14" s="19">
         <f>E14*1.10</f>
-        <v/>
+        <v>24.200000000000003</v>
       </c>
       <c r="G14" s="19">
         <f>E14-$C$4</f>
-        <v/>
+        <v>16.5</v>
       </c>
     </row>
     <row r="15">
@@ -936,19 +961,28 @@
         <v>0.25</v>
       </c>
       <c r="E15" s="15">
-        <f>$C$4/=AVERAGE(C15,D15)</f>
-        <v/>
+        <f>$C$4/AVERAGE(C15,D15)</f>
+        <v>25.58139534883721</v>
       </c>
       <c r="F15" s="15">
         <f>E15*1.10</f>
-        <v/>
+        <v>28.13953488372093</v>
       </c>
       <c r="G15" s="15">
         <f>E15-$C$4</f>
-        <v/>
+        <v>20.08139534883721</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-escandallos/10-calculadora-pvp.xlsx
+++ b/astro-site/public/dl/kit-escandallos/10-calculadora-pvp.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calculadora PVP'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Calculadora PVP'!$A$1:$J$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +93,30 @@
       <color rgb="00333333"/>
       <sz val="11"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00606060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -130,8 +153,33 @@
         <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -153,11 +201,55 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -199,6 +291,59 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -597,66 +742,164 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cómo usar esta plantilla</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>▸ Escribe en la celda verde (C4) el coste de UNA ración. Sale de la plantilla de escandallo: es la fila «COSTE POR RACIÓN» en 01-04 y 06-08, y «COSTE POR UNIDAD» en 05-pastelería. NO el «COSTE TOTAL DE LA TANDA»: en pastelería difieren por 12, 20 o 30.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>▸ La tabla calcula el PVP para cada tipo de establecimiento. Sólo se escriben las celdas VERDES.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>▸ Introduce el coste total de tu plato en la celda verde</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>▸ La tabla calcula automáticamente el PVP para cada tipo de establecimiento</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Qué es cada columna</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>▸ Cada tipo tiene su food cost objetivo y multiplicador</t>
-        </is>
-      </c>
+      <c r="B10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>▸ Los PVP incluyen versión sin IVA y con IVA (10%)</t>
+          <t>▸ Food Cost mín. / máx.: la horquilla de food cost objetivo de ese tipo de negocio. Editable.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>▸ Multiplicador: 1 ÷ media de la horquilla. Es el número por el que multiplicas el coste para sacar el PVP — el atajo que se usa en cocina.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>▸ Comisión plataforma (%): lo que se queda el intermediario. Se descuenta ANTES de calcular el precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>▸ PVP sin IVA: coste × multiplicador ÷ (1 − comisión).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>▸ PVP con IVA: el anterior por el tipo de IVA de C5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>▸ Ingreso neto tras comisión: lo que te ingresa la plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>▸ Margen neto: ingreso neto − coste del plato. Es el dinero que te queda de verdad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>▸ Es la fila que más se equivoca todo el mundo. Aplicar el PVP de «Casual Dining» a una carta de Glovo o Uber Eats significa regalar la comisión: con un 30 % de comisión, un plato de 18 € deja 12,60 €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>▸ Su food cost objetivo (28-32 %) se mide sobre el ingreso NETO, ya descontada la comisión. Un 30 % sobre neto equivale a un ~21 % sobre el PVP bruto: por eso el precio de la carta de delivery sale alto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>▸ Si vendes por tu propia web o con reparto propio, pon la comisión a 0 % y usa el food cost de tu tipo de local.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de IVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>▸ C5 es editable: 10 % en hostelería en España. Cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>▸ La hoja está protegida SIN contraseña: sólo se escriben las celdas verdes. Revisar → Desproteger hoja para tocar el resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="36"/>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -684,296 +927,570 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="20" t="n"/>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="20" t="n"/>
+    </row>
     <row r="2">
-      <c r="B2" s="9" t="inlineStr">
+      <c r="A2" s="20" t="n"/>
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Calculadora de PVP Sugerido</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="20" t="n"/>
+    </row>
     <row r="4">
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>COSTE TOTAL DEL PLATO (€):</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
+      <c r="A4" s="20" t="n"/>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>COSTE POR RACIÓN / POR UNIDAD (€):</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Tipo Establecimiento</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Food Cost Min</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Food Cost Max</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Tipo de IVA (%):</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="20" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="20" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>El IVA es una celda: 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país). El «Multiplicador» es 1 ÷ media del rango de food cost: es el número por el que multiplicas el coste para sacar el PVP.</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="20" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="20" t="n"/>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Tipo de establecimiento</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Food Cost mín.</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Food Cost máx.</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Multiplicador</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>Comisión plataforma (%)</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>PVP sin IVA (€)</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>PVP con IVA (€)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Margen (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="13" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>Ingreso neto tras comisión (€)</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>Margen neto (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Fine Dining</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C9" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D9" s="32" t="n">
         <v>0.28</v>
       </c>
-      <c r="E7" s="15">
-        <f>$C$4/AVERAGE(C7,D7)</f>
+      <c r="E9" s="33">
+        <f>IFERROR(1/AVERAGE(C9,D9),"")</f>
+        <v>3.773584905660377</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="34">
+        <f>IFERROR($C$4*E9/(1-F9),"")</f>
         <v>20.754716981132074</v>
       </c>
-      <c r="F7" s="16">
-        <f>E7*1.10</f>
+      <c r="H9" s="35">
+        <f>IFERROR(G9*(1+$C$5),"")</f>
         <v>22.830188679245282</v>
       </c>
-      <c r="G7" s="15">
-        <f>E7-$C$4</f>
+      <c r="I9" s="36">
+        <f>IFERROR(G9*(1-F9),"")</f>
+        <v>20.754716981132074</v>
+      </c>
+      <c r="J9" s="36">
+        <f>IFERROR(I9-$C$4,"")</f>
         <v>15.254716981132074</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Casual Dining</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C10" s="32" t="n">
         <v>0.28</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D10" s="32" t="n">
         <v>0.32</v>
       </c>
-      <c r="E8" s="19">
-        <f>$C$4/AVERAGE(C8,D8)</f>
+      <c r="E10" s="38">
+        <f>IFERROR(1/AVERAGE(C10,D10),"")</f>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="39">
+        <f>IFERROR($C$4*E10/(1-F10),"")</f>
         <v>18.333333333333332</v>
       </c>
-      <c r="F8" s="19">
-        <f>E8*1.10</f>
+      <c r="H10" s="35">
+        <f>IFERROR(G10*(1+$C$5),"")</f>
         <v>20.166666666666668</v>
       </c>
-      <c r="G8" s="19">
-        <f>E8-$C$4</f>
+      <c r="I10" s="40">
+        <f>IFERROR(G10*(1-F10),"")</f>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="J10" s="40">
+        <f>IFERROR(I10-$C$4,"")</f>
         <v>12.833333333333332</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Fast Casual</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C11" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D11" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E9" s="15">
-        <f>$C$4/AVERAGE(C9,D9)</f>
+      <c r="E11" s="33">
+        <f>IFERROR(1/AVERAGE(C11,D11),"")</f>
+        <v>3.0769230769230775</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="34">
+        <f>IFERROR($C$4*E11/(1-F11),"")</f>
         <v>16.923076923076927</v>
       </c>
-      <c r="F9" s="15">
-        <f>E9*1.10</f>
+      <c r="H11" s="35">
+        <f>IFERROR(G11*(1+$C$5),"")</f>
         <v>18.61538461538462</v>
       </c>
-      <c r="G9" s="15">
-        <f>E9-$C$4</f>
+      <c r="I11" s="36">
+        <f>IFERROR(G11*(1-F11),"")</f>
+        <v>16.923076923076927</v>
+      </c>
+      <c r="J11" s="36">
+        <f>IFERROR(I11-$C$4,"")</f>
         <v>11.423076923076927</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Cafetería</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C12" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D12" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="E10" s="19">
-        <f>$C$4/AVERAGE(C10,D10)</f>
+      <c r="E12" s="38">
+        <f>IFERROR(1/AVERAGE(C12,D12),"")</f>
+        <v>3.6363636363636362</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39">
+        <f>IFERROR($C$4*E12/(1-F12),"")</f>
         <v>20.0</v>
       </c>
-      <c r="F10" s="19">
-        <f>E10*1.10</f>
+      <c r="H12" s="35">
+        <f>IFERROR(G12*(1+$C$5),"")</f>
         <v>22.0</v>
       </c>
-      <c r="G10" s="19">
-        <f>E10-$C$4</f>
+      <c r="I12" s="40">
+        <f>IFERROR(G12*(1-F12),"")</f>
+        <v>20.0</v>
+      </c>
+      <c r="J12" s="40">
+        <f>IFERROR(I12-$C$4,"")</f>
         <v>14.5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Catering</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C13" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D13" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" s="15">
-        <f>$C$4/AVERAGE(C11,D11)</f>
+      <c r="E13" s="33">
+        <f>IFERROR(1/AVERAGE(C13,D13),"")</f>
+        <v>2.857142857142857</v>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="34">
+        <f>IFERROR($C$4*E13/(1-F13),"")</f>
         <v>15.714285714285715</v>
       </c>
-      <c r="F11" s="15">
-        <f>E11*1.10</f>
+      <c r="H13" s="35">
+        <f>IFERROR(G13*(1+$C$5),"")</f>
         <v>17.28571428571429</v>
       </c>
-      <c r="G11" s="15">
-        <f>E11-$C$4</f>
+      <c r="I13" s="36">
+        <f>IFERROR(G13*(1-F13),"")</f>
+        <v>15.714285714285715</v>
+      </c>
+      <c r="J13" s="36">
+        <f>IFERROR(I13-$C$4,"")</f>
         <v>10.214285714285715</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Food Truck</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C14" s="32" t="n">
         <v>0.28</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D14" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E12" s="19">
-        <f>$C$4/AVERAGE(C12,D12)</f>
+      <c r="E14" s="38">
+        <f>IFERROR(1/AVERAGE(C14,D14),"")</f>
+        <v>3.1746031746031744</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="39">
+        <f>IFERROR($C$4*E14/(1-F14),"")</f>
         <v>17.46031746031746</v>
       </c>
-      <c r="F12" s="19">
-        <f>E12*1.10</f>
+      <c r="H14" s="35">
+        <f>IFERROR(G14*(1+$C$5),"")</f>
         <v>19.206349206349206</v>
       </c>
-      <c r="G12" s="19">
-        <f>E12-$C$4</f>
+      <c r="I14" s="40">
+        <f>IFERROR(G14*(1-F14),"")</f>
+        <v>17.46031746031746</v>
+      </c>
+      <c r="J14" s="40">
+        <f>IFERROR(I14-$C$4,"")</f>
         <v>11.960317460317459</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="20" t="n"/>
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Hotel F&amp;B</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C15" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D15" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E13" s="15">
-        <f>$C$4/AVERAGE(C13,D13)</f>
+      <c r="E15" s="33">
+        <f>IFERROR(1/AVERAGE(C15,D15),"")</f>
+        <v>3.0769230769230775</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="34">
+        <f>IFERROR($C$4*E15/(1-F15),"")</f>
         <v>16.923076923076927</v>
       </c>
-      <c r="F13" s="15">
-        <f>E13*1.10</f>
+      <c r="H15" s="35">
+        <f>IFERROR(G15*(1+$C$5),"")</f>
         <v>18.61538461538462</v>
       </c>
-      <c r="G13" s="15">
-        <f>E13-$C$4</f>
+      <c r="I15" s="36">
+        <f>IFERROR(G15*(1-F15),"")</f>
+        <v>16.923076923076927</v>
+      </c>
+      <c r="J15" s="36">
+        <f>IFERROR(I15-$C$4,"")</f>
         <v>11.423076923076927</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="20" t="n"/>
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>Pastelería</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C16" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D16" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="E14" s="19">
-        <f>$C$4/AVERAGE(C14,D14)</f>
+      <c r="E16" s="42">
+        <f>IFERROR(1/AVERAGE(C16,D16),"")</f>
+        <v>4.0</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="43">
+        <f>IFERROR($C$4*E16/(1-F16),"")</f>
         <v>22.0</v>
       </c>
-      <c r="F14" s="19">
-        <f>E14*1.10</f>
+      <c r="H16" s="35">
+        <f>IFERROR(G16*(1+$C$5),"")</f>
         <v>24.200000000000003</v>
       </c>
-      <c r="G14" s="19">
-        <f>E14-$C$4</f>
+      <c r="I16" s="40">
+        <f>IFERROR(G16*(1-F16),"")</f>
+        <v>22.0</v>
+      </c>
+      <c r="J16" s="40">
+        <f>IFERROR(I16-$C$4,"")</f>
         <v>16.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Bar/Cocktails</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D15" s="14" t="n">
+    <row r="17">
+      <c r="A17" s="20" t="n"/>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>Bar/Cócteles</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" s="15">
-        <f>$C$4/AVERAGE(C15,D15)</f>
-        <v>25.58139534883721</v>
-      </c>
-      <c r="F15" s="15">
-        <f>E15*1.10</f>
-        <v>28.13953488372093</v>
-      </c>
-      <c r="G15" s="15">
-        <f>E15-$C$4</f>
-        <v>20.08139534883721</v>
+      <c r="E17" s="45">
+        <f>IFERROR(1/AVERAGE(C17,D17),"")</f>
+        <v>4.444444444444445</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="46">
+        <f>IFERROR($C$4*E17/(1-F17),"")</f>
+        <v>24.444444444444446</v>
+      </c>
+      <c r="H17" s="35">
+        <f>IFERROR(G17*(1+$C$5),"")</f>
+        <v>26.888888888888893</v>
+      </c>
+      <c r="I17" s="36">
+        <f>IFERROR(G17*(1-F17),"")</f>
+        <v>24.444444444444446</v>
+      </c>
+      <c r="J17" s="36">
+        <f>IFERROR(I17-$C$4,"")</f>
+        <v>18.944444444444446</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E18" s="42">
+        <f>IFERROR(1/AVERAGE(C18,D18),"")</f>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="43">
+        <f>IFERROR($C$4*E18/(1-F18),"")</f>
+        <v>26.19047619047619</v>
+      </c>
+      <c r="H18" s="35">
+        <f>IFERROR(G18*(1+$C$5),"")</f>
+        <v>28.80952380952381</v>
+      </c>
+      <c r="I18" s="40">
+        <f>IFERROR(G18*(1-F18),"")</f>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="J18" s="40">
+        <f>IFERROR(I18-$C$4,"")</f>
+        <v>12.833333333333332</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="20" t="n"/>
+      <c r="J19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Delivery: la comisión de la plataforma (25-35 %) se descuenta ANTES de calcular el precio, así que el PVP de la carta de delivery sale muy por encima del de sala — es la única forma de que te quede el mismo dinero en el bolsillo. Su food cost objetivo (28-32 %) se mide sobre el INGRESO NETO, no sobre el precio de la carta: un 30 % sobre neto equivale a un ~21 % sobre el PVP bruto, y por eso el precio de delivery sube. Si vendes por tu propia web, pon la comisión a 0 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>La comisión funciona en TODAS las filas: si trabajas una carta de sala también en plataforma, copia el food cost de tu fila y pon la comisión que te cobren.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="4">
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
